--- a/TESTS/zlit_6_o_henri.xlsx
+++ b/TESTS/zlit_6_o_henri.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -603,6 +608,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Вільям Сідні Портер — О. Генрі псевдонім якого він почав користуватись під час перебування у в'язниці</t>
+          <t>Вільям Сідні Портер</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Несподіваний дотепний фінал що перевертає сприйняття всього попереднього — «поворот О. Генрі»</t>
+          <t>Несподіваний дотепний фінал що перевертає сприйняття всього попереднього</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -813,6 +843,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,6 +890,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Він знав свого сина — хлопчик настільки нестерпний що вигнав батька з дому і той хотів позбутись його якомога довше</t>
+          <t>Він знав свого сина</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Злочин не завжди окупається — іноді «жертва» виявляється гіршим покаранням ніж будь-яке слідство</t>
+          <t>Злочин не завжди окупається</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Яке ім'я дав собі хлопчик Джонні, граючись у викрадачів?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Робін Гуд</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>«Вождь Червоношкірих», що «бере в полон» своїх викрадачів</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Капітан Крюк</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Шериф</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що Джонні робив з одним із викрадачів, удаючи, що «здирає скальп»?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не робив</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сідав на нього зверху і вдавав, що знімає скальп, смикаючи за волосся</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зв'язав його</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Намалював на ньому фарбою</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому викрадачі не могли навіть нормально поспати вночі?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Було занадто гучно ззовні</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Джонні весь час будив їх, граючись, кричав і вимагав уваги</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони боялись поліції</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Було занадто холодно</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Скільки грошей спочатку зажадали викрадачі за повернення хлопчика?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Тисячу доларів</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дві тисячі доларів</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>П'ятсот доларів</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>П'ять тисяч доларів</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як Джонні поставився до новини про те, що його скоро «врятують» додому?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зрадів і запакував речі</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Розплакався і не хотів іти додому, кажучи, що йому весело з викрадачами</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Втік сам</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не повірив у це</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Яку звичну вимогу містив лист про викуп, окрім суми грошей?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вимогу публікації в газеті</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вимогу не звертатися в поліцію і залишити гроші у визначеному місці</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вимогу особистої зустрічі</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого більше не вимагали</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Як батько Джонні (Ебенезер Доуз) відповів на лист з вимогою викупу?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу погодився заплатити</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Написав контрпропозицію — погодиться забрати сина лише за додаткову плату самим викрадачам</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Викликав поліцію</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Проігнорував лист</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Скільки грошей батько в результаті зажадав із викрадачів за те, щоб забрати сина назад?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого не зажадав</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>250 доларів</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>1000 доларів</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>50 доларів</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Чому викрадачі, попри обурення, зрештою погодились на умови батька?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони злякались поліції</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Джонні був для них таким тягарем, що будь-яка плата здавалась виправданою, аби позбутися його</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Батько їм погрожував</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони не мали вибору юридично</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Скільки грошей мала Делла напередодні Різдва, щоб купити подарунок чоловікові?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Достатньо для гарного подарунка</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Лише один долар і вісімдесят сім центів, заощаджених по копійці</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сто доларів</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого зовсім</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Якою описана квартира, де жили Делла і Джим?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Велика й розкішна</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Скромна, недорога квартирка, де навіть дзвінок не працював належно</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Будинок у передмісті</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Готельний номер</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Чому подарунок для Джима був для Делли особливо важливим попри бідність?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Це була традиція</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона хотіла довести своє кохання гідним подарунком, навіть якщо доведеться чимось пожертвувати</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Джим вимагав подарунок</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Це був заклад</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Чим особливо славилось подружжя Джеймс Діллінгем Янг, попри бідність — два «скарби»?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Картини й книги</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чудове густе волосся Делли і золотий кишеньковий годинник Джима — родинна реліквія</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Будинок і сад</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Колекція монет</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Що Делла зробила зі своїм прекрасним волоссям заради подарунка Джиму?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заплела у косу і сховала</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Продала його перукарю за двадцять доларів</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пофарбувала</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Подарувала подрузі</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що Делла купила Джиму на отримані за волосся гроші?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Шапку</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Платиновий ланцюжок для його дорогоцінного кишенькового годинника</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Краватку</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Книгу</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Як Джим відреагував, побачивши, що Делла відрізала своє волосся?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розгнівався</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Застиг у дивному, незрозумілому Делли вираженні, не сердячись, але й не радіючи одразу</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розсміявся</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не помітив</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Що Джим подарував Делли на Різдво, і чому це стало несподіванкою?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нову сукню — звичний подарунок</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дорогі гребінці для волосся — якраз тоді, коли вона щойно продала своє волосся</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Кільце</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Парфуми</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Що виявилось із подарунком Джима наприкінці оповідання?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Джим теж купив ланцюжок</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Джим продав свій годинник, щоб купити Делли гребінці — тож ланцюжок Делли тепер не до чого носити</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подарунки виявились однаковими</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Джим нічого не подарував</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Чому О. Генрі називає Деллу і Джима «волхвами» наприкінці оповідання?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони були мудрецями за фахом</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Як біблійні волхви, що принесли дари младенцю Христу, вони віддали найцінніше, що мали, з любові</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони подорожували з Сходу</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони носили коштовності</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>У чому, за словами оповідача, полягає парадокс подарунків Делли і Джима?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Подарунки були однакові</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Обидва подарунки практично втратили миттєву користь, але стали найціннішими саме через це</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подарунки були занадто дорогі</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Подарунки не сподобались</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Яка головна ідея «Дарів волхвів»?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гроші — найважливіше у стосунках</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Найбільша мудрість і цінність дару — у самопожертві й любові, з якою його даровано</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Треба завжди купувати практичні подарунки</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бідність руйнує кохання</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між двома оповіданнями О. Генрі у програмі?</t>
+          <t>В обох оповіданнях О. Генрі поєднує гумор з несподіваним, по-справжньому людяним фіналом.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку соціальну тему порушує «Дари волхвів»?</t>
+          <t>«Дари волхвів» порушують тему бідності молодого подружжя, яке попри нестачу грошей знаходить спосіб виявити любов.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чому гумор О. Генрі у «Вожді червоношкірих» є особливим?</t>
+          <t>Гумор у «Вожді червоношкірих» побудований лише на діалогах дорослих, без участі самого хлопчика.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>У чому несподіваний фінал «Дарів волхвів»?</t>
+          <t>Несподіваний фінал «Дарів волхвів» — обидва подарунки практично втратили миттєву користь, але саме це робить їх найціннішими проявами любові.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Чому О. Генрі називає Деллу і Джима «волхвами»?</t>
+          <t>О. Генрі називає Деллу і Джима «найглупішими» людьми, що марно витратили гроші.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Дарів волхвів»?</t>
+          <t>Головна ідея «Дарів волхвів» — справжня цінність подарунка вимірюється грошима, які на нього витрачено.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси оповідань О. Генрі виявляються в обох творах?</t>
+          <t>Що сталося в обох оповіданнях?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Несподіваний фінал</t>
+          <t>У «Вожді» батько вимагав гроші з викрадачів</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Гумор і парадокс</t>
+          <t>У «Дарах волхвів» Делла продала волосся</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Детективний сюжет</t>
+          <t>Хлопчика в «Вожді» легко налякали</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Яскраві живі персонажі</t>
+          <t>Джим продав годинник</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Молоде бідне подружжя Делла і Джим — напередодні Різдва у них майже немає грошей на подарунки</t>
+          <t>Молоде бідне подружжя Делла і Джим</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Продала свої прекрасні довгі коси — найцінніше що вона мала — щоб купити ланцюжок до годинника Джима</t>
+          <t>Продала свої прекрасні довгі коси</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Продав свій родинний годинник яким пишався — щоб купити розкішні гребені для кіс Делли</t>
+          <t>Продав свій родинний годинник яким пишався</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
